--- a/КС-2_КС-3_№1_витражи_лит4_70%_ВДЦ.xlsx
+++ b/КС-2_КС-3_№1_витражи_лит4_70%_ВДЦ.xlsx
@@ -9,9 +9,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="КС-2 " sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="КС-3" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'КС-2 '!$A$35:$J$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'КС-2 '!$A$1:$AG$215</definedName>
@@ -2577,627 +2574,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Расшифровка по КП"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>А</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>Вн-6</v>
-          </cell>
-          <cell r="J5">
-            <v>3</v>
-          </cell>
-          <cell r="K5">
-            <v>59.76</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>А</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>Вн-8</v>
-          </cell>
-          <cell r="J6">
-            <v>1</v>
-          </cell>
-          <cell r="K6">
-            <v>12.34</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>А</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>Вн-15</v>
-          </cell>
-          <cell r="J7">
-            <v>1</v>
-          </cell>
-          <cell r="K7">
-            <v>5.62</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>А</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>Вн-14</v>
-          </cell>
-          <cell r="J8">
-            <v>1</v>
-          </cell>
-          <cell r="K8">
-            <v>11.14</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>Вн-6</v>
-          </cell>
-          <cell r="J9">
-            <v>1</v>
-          </cell>
-          <cell r="K9">
-            <v>19.39</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>Вн-17</v>
-          </cell>
-          <cell r="J10">
-            <v>1</v>
-          </cell>
-          <cell r="K10">
-            <v>19.489999999999998</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>Вн-6</v>
-          </cell>
-          <cell r="J11">
-            <v>1</v>
-          </cell>
-          <cell r="K11">
-            <v>19.489999999999998</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>Вн-15</v>
-          </cell>
-          <cell r="J12">
-            <v>1</v>
-          </cell>
-          <cell r="K12">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>Вн-18</v>
-          </cell>
-          <cell r="J13">
-            <v>1</v>
-          </cell>
-          <cell r="K13">
-            <v>11.9</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>Вн-6</v>
-          </cell>
-          <cell r="J14">
-            <v>1</v>
-          </cell>
-          <cell r="K14">
-            <v>19.579999999999998</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>В</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>Вн-6</v>
-          </cell>
-          <cell r="J15">
-            <v>1</v>
-          </cell>
-          <cell r="K15">
-            <v>19.63</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>В</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>Вн-16</v>
-          </cell>
-          <cell r="J16">
-            <v>1</v>
-          </cell>
-          <cell r="K16">
-            <v>5.95</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>В</v>
-          </cell>
-          <cell r="C17" t="str">
-            <v>Вн-19</v>
-          </cell>
-          <cell r="J17">
-            <v>2</v>
-          </cell>
-          <cell r="K17">
-            <v>24.67</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>Г</v>
-          </cell>
-          <cell r="C18" t="str">
-            <v>Вн-10</v>
-          </cell>
-          <cell r="J18">
-            <v>1</v>
-          </cell>
-          <cell r="K18">
-            <v>20.16</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>Д</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>Вн-9</v>
-          </cell>
-          <cell r="J19">
-            <v>1</v>
-          </cell>
-          <cell r="K19">
-            <v>19.68</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>Д</v>
-          </cell>
-          <cell r="C20" t="str">
-            <v>Вн-17</v>
-          </cell>
-          <cell r="J20">
-            <v>1</v>
-          </cell>
-          <cell r="K20">
-            <v>18.14</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>Д</v>
-          </cell>
-          <cell r="C21" t="str">
-            <v>Вн-6</v>
-          </cell>
-          <cell r="J21">
-            <v>1</v>
-          </cell>
-          <cell r="K21">
-            <v>19.87</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>Д</v>
-          </cell>
-          <cell r="C22" t="str">
-            <v>Вн-7</v>
-          </cell>
-          <cell r="J22">
-            <v>1</v>
-          </cell>
-          <cell r="K22">
-            <v>19.97</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>Д</v>
-          </cell>
-          <cell r="C23" t="str">
-            <v>Вн-6</v>
-          </cell>
-          <cell r="J23">
-            <v>1</v>
-          </cell>
-          <cell r="K23">
-            <v>20.11</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>А</v>
-          </cell>
-          <cell r="C24" t="str">
-            <v>Вн-22</v>
-          </cell>
-          <cell r="J24">
-            <v>5</v>
-          </cell>
-          <cell r="K24">
-            <v>28.57</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C25" t="str">
-            <v>Вн-22</v>
-          </cell>
-          <cell r="J25">
-            <v>5</v>
-          </cell>
-          <cell r="K25">
-            <v>28.57</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>В</v>
-          </cell>
-          <cell r="C26" t="str">
-            <v>Вн-22</v>
-          </cell>
-          <cell r="J26">
-            <v>1</v>
-          </cell>
-          <cell r="K26">
-            <v>5.71</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>В</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v>Вн-13</v>
-          </cell>
-          <cell r="J27">
-            <v>1</v>
-          </cell>
-          <cell r="K27">
-            <v>14.74</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>А</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>Вн-6</v>
-          </cell>
-          <cell r="J28">
-            <v>1</v>
-          </cell>
-          <cell r="K28">
-            <v>19.82</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>Г</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v>Вн-17</v>
-          </cell>
-          <cell r="J29">
-            <v>1</v>
-          </cell>
-          <cell r="K29">
-            <v>19.82</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>Г</v>
-          </cell>
-          <cell r="C30" t="str">
-            <v>Вн-21</v>
-          </cell>
-          <cell r="J30">
-            <v>1</v>
-          </cell>
-          <cell r="K30">
-            <v>14.02</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>Г</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v>Вн-6</v>
-          </cell>
-          <cell r="J31">
-            <v>1</v>
-          </cell>
-          <cell r="K31">
-            <v>20.45</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>Г</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>Вн-20</v>
-          </cell>
-          <cell r="J32">
-            <v>1</v>
-          </cell>
-          <cell r="K32">
-            <v>18.43</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>Г</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>Вн-12</v>
-          </cell>
-          <cell r="J33">
-            <v>1</v>
-          </cell>
-          <cell r="K33">
-            <v>15.6</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>Г</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>Вн-11</v>
-          </cell>
-          <cell r="J34">
-            <v>1</v>
-          </cell>
-          <cell r="K34">
-            <v>11.09</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>Вн-6</v>
-          </cell>
-          <cell r="J35">
-            <v>1</v>
-          </cell>
-          <cell r="K35">
-            <v>19.82</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>А</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J36">
-            <v>3</v>
-          </cell>
-          <cell r="K36">
-            <v>9.75</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="str">
-            <v>А</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J37">
-            <v>1</v>
-          </cell>
-          <cell r="K37">
-            <v>3.25</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="str">
-            <v>А</v>
-          </cell>
-          <cell r="C38" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J38">
-            <v>1</v>
-          </cell>
-          <cell r="K38">
-            <v>2.69</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J39">
-            <v>3</v>
-          </cell>
-          <cell r="K39">
-            <v>9.75</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J40">
-            <v>1</v>
-          </cell>
-          <cell r="K40">
-            <v>3.25</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41" t="str">
-            <v>Б</v>
-          </cell>
-          <cell r="C41" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J41">
-            <v>1</v>
-          </cell>
-          <cell r="K41">
-            <v>2.89</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42" t="str">
-            <v>В</v>
-          </cell>
-          <cell r="C42" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J42">
-            <v>1</v>
-          </cell>
-          <cell r="K42">
-            <v>3.25</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43" t="str">
-            <v>В</v>
-          </cell>
-          <cell r="C43" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J43">
-            <v>2</v>
-          </cell>
-          <cell r="K43">
-            <v>6.5</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44" t="str">
-            <v>В</v>
-          </cell>
-          <cell r="C44" t="str">
-            <v>Д35</v>
-          </cell>
-          <cell r="J44">
-            <v>1</v>
-          </cell>
-          <cell r="K44">
-            <v>2.86</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45" t="str">
-            <v>Г</v>
-          </cell>
-          <cell r="C45" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J45">
-            <v>1</v>
-          </cell>
-          <cell r="K45">
-            <v>3.25</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46" t="str">
-            <v>Д</v>
-          </cell>
-          <cell r="C46" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J46">
-            <v>2</v>
-          </cell>
-          <cell r="K46">
-            <v>6.5</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47" t="str">
-            <v>Д</v>
-          </cell>
-          <cell r="C47" t="str">
-            <v>Д17</v>
-          </cell>
-          <cell r="J47">
-            <v>1</v>
-          </cell>
-          <cell r="K47">
-            <v>3.25</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="K48">
-            <v>626.72</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
